--- a/budget-tracker.xlsx
+++ b/budget-tracker.xlsx
@@ -3007,13 +3007,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{706CC1CA-CD82-47B4-AB9A-028732F0EE0A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148B4A59-7D80-4037-9192-5DB9B5E3AE0F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{623E86E9-5546-4E65-B1E7-5314ED0B61C6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48762FCA-4FD5-4A43-942F-64045CF3F439}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26CB3EE6-377C-4D0F-AD43-257E12103E76}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16CCAF9B-ABDF-4503-8407-FB18D1AEA01A}"/>
 </file>